--- a/02 - Excel Intermediario/Exercicios/IP - EX 38 - Graficos Avancados.xlsx
+++ b/02 - Excel Intermediario/Exercicios/IP - EX 38 - Graficos Avancados.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cliente\Desktop\excel novos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizh\Desktop\Cursos\DNC\Cientista de Dados - DNC\02 - Excel Intermediario\Exercicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A6D123-7317-4AF7-B3BD-DF3CCECF6111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="60" windowWidth="20115" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONTEÚDO" sheetId="1" r:id="rId1"/>
@@ -17,12 +18,26 @@
     <sheet name="EXERCÍCIOS" sheetId="5" r:id="rId3"/>
     <sheet name="EXERCÍCIOS (resolvido)" sheetId="6" state="hidden" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="54">
   <si>
     <t>CONTEÚDO DA AULA</t>
   </si>
@@ -189,7 +204,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -921,7 +936,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -932,6 +950,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -947,12 +968,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -974,6 +989,325 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Janeiro</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>EXPLICAÇÃO!$B$11:$B$14</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>joão</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>fernanda</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>thiago</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>maria</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>EXPLICAÇÃO!$D$11:$D$14</c:f>
+              <c:numCache>
+                <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>365</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-F859-423A-B865-966A32A6C906}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Fevereiro</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>EXPLICAÇÃO!$B$11:$B$14</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>joão</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>fernanda</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>thiago</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>maria</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>EXPLICAÇÃO!$D$15:$D$18</c:f>
+              <c:numCache>
+                <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>123</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>459</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>133</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-F859-423A-B865-966A32A6C906}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="2031824815"/>
+        <c:axId val="2031832719"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2031824815"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2031832719"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2031832719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2031824815"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -1398,6 +1732,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1940,6 +2314,509 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -1957,7 +2834,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagem 1" descr="LOGO.bmp"/>
+        <xdr:cNvPr id="2" name="Imagem 1" descr="LOGO.bmp">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2000,7 +2883,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagem 1" descr="LOGO.bmp"/>
+        <xdr:cNvPr id="2" name="Imagem 1" descr="LOGO.bmp">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2023,6 +2912,42 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E5E62BC-BE42-444A-A0F0-7F50F5CAE8AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2043,7 +2968,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagem 1" descr="LOGO.bmp"/>
+        <xdr:cNvPr id="2" name="Imagem 1" descr="LOGO.bmp">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2081,7 +3012,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2" descr="http://www.pepsico.com.br/images/logo_pepsico.png"/>
+        <xdr:cNvPr id="3" name="Imagem 2" descr="http://www.pepsico.com.br/images/logo_pepsico.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -2141,7 +3078,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagem 1" descr="LOGO.bmp"/>
+        <xdr:cNvPr id="2" name="Imagem 1" descr="LOGO.bmp">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2179,7 +3122,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2" descr="http://www.pepsico.com.br/images/logo_pepsico.png"/>
+        <xdr:cNvPr id="3" name="Imagem 2" descr="http://www.pepsico.com.br/images/logo_pepsico.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -2234,7 +3183,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Gráfico 3"/>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2328,6 +3283,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -2363,6 +3335,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2538,7 +3527,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:Q11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2664,7 +3653,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:Q18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2881,7 +3870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:T36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3032,12 +4021,14 @@
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B13" s="17"/>
-      <c r="M13" s="85" t="s">
+      <c r="M13" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="N13" s="85"/>
-      <c r="O13" s="86"/>
-      <c r="P13" s="86"/>
+      <c r="N13" s="76"/>
+      <c r="O13" s="77" t="s">
+        <v>37</v>
+      </c>
+      <c r="P13" s="77"/>
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3131,7 +4122,7 @@
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B16" s="77" t="s">
+      <c r="B16" s="78" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="24" t="s">
@@ -3173,10 +4164,13 @@
       <c r="O16" s="50">
         <v>12</v>
       </c>
-      <c r="P16" s="25"/>
+      <c r="P16" s="25">
+        <f>SUBTOTAL(_xlfn.XLOOKUP($O$13, $S$19:$S$27, $T$19:$T$27), D16:O16)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B17" s="78"/>
+      <c r="B17" s="79"/>
       <c r="C17" s="26" t="s">
         <v>31</v>
       </c>
@@ -3216,11 +4210,14 @@
       <c r="O17" s="52">
         <v>9</v>
       </c>
-      <c r="P17" s="27"/>
+      <c r="P17" s="27">
+        <f t="shared" ref="P17:P32" si="0">SUBTOTAL(_xlfn.XLOOKUP($O$13, $S$19:$S$27, $T$19:$T$27), D17:O17)</f>
+        <v>10.25</v>
+      </c>
       <c r="Q17" s="28"/>
     </row>
     <row r="18" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="79"/>
+      <c r="B18" s="80"/>
       <c r="C18" s="29" t="s">
         <v>33</v>
       </c>
@@ -3260,7 +4257,10 @@
       <c r="O18" s="54">
         <v>5</v>
       </c>
-      <c r="P18" s="30"/>
+      <c r="P18" s="30">
+        <f t="shared" si="0"/>
+        <v>7.25</v>
+      </c>
       <c r="Q18" s="28"/>
       <c r="S18" s="31" t="s">
         <v>34</v>
@@ -3270,7 +4270,7 @@
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B19" s="77" t="s">
+      <c r="B19" s="78" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="32" t="str">
@@ -3313,7 +4313,10 @@
       <c r="O19" s="50">
         <v>8</v>
       </c>
-      <c r="P19" s="25"/>
+      <c r="P19" s="25">
+        <f t="shared" si="0"/>
+        <v>11.416666666666666</v>
+      </c>
       <c r="Q19" s="28"/>
       <c r="S19" s="33" t="s">
         <v>37</v>
@@ -3323,9 +4326,9 @@
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B20" s="78"/>
+      <c r="B20" s="79"/>
       <c r="C20" s="34" t="str">
-        <f t="shared" ref="C20:C27" si="0">IF(C17="","NA",C17)</f>
+        <f t="shared" ref="C20:C27" si="1">IF(C17="","NA",C17)</f>
         <v>Maria</v>
       </c>
       <c r="D20" s="51">
@@ -3364,7 +4367,10 @@
       <c r="O20" s="52">
         <v>18</v>
       </c>
-      <c r="P20" s="27"/>
+      <c r="P20" s="27">
+        <f t="shared" si="0"/>
+        <v>10.25</v>
+      </c>
       <c r="Q20" s="28"/>
       <c r="S20" s="33" t="s">
         <v>38</v>
@@ -3374,9 +4380,9 @@
       </c>
     </row>
     <row r="21" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="79"/>
+      <c r="B21" s="80"/>
       <c r="C21" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Ana</v>
       </c>
       <c r="D21" s="53">
@@ -3415,7 +4421,10 @@
       <c r="O21" s="54">
         <v>18</v>
       </c>
-      <c r="P21" s="30"/>
+      <c r="P21" s="30">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
       <c r="Q21" s="28"/>
       <c r="S21" s="33" t="s">
         <v>39</v>
@@ -3425,7 +4434,7 @@
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B22" s="77" t="s">
+      <c r="B22" s="78" t="s">
         <v>40</v>
       </c>
       <c r="C22" s="32" t="str">
@@ -3468,7 +4477,10 @@
       <c r="O22" s="50">
         <v>12</v>
       </c>
-      <c r="P22" s="25"/>
+      <c r="P22" s="25">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
       <c r="Q22" s="28"/>
       <c r="S22" s="33" t="s">
         <v>41</v>
@@ -3478,9 +4490,9 @@
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B23" s="78"/>
+      <c r="B23" s="79"/>
       <c r="C23" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Maria</v>
       </c>
       <c r="D23" s="51">
@@ -3519,7 +4531,10 @@
       <c r="O23" s="52">
         <v>15</v>
       </c>
-      <c r="P23" s="27"/>
+      <c r="P23" s="27">
+        <f t="shared" si="0"/>
+        <v>10.916666666666666</v>
+      </c>
       <c r="Q23" s="28"/>
       <c r="S23" s="33" t="s">
         <v>42</v>
@@ -3529,9 +4544,9 @@
       </c>
     </row>
     <row r="24" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="79"/>
+      <c r="B24" s="80"/>
       <c r="C24" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Ana</v>
       </c>
       <c r="D24" s="53">
@@ -3570,7 +4585,10 @@
       <c r="O24" s="54">
         <v>6</v>
       </c>
-      <c r="P24" s="30"/>
+      <c r="P24" s="30">
+        <f t="shared" si="0"/>
+        <v>10.916666666666666</v>
+      </c>
       <c r="Q24" s="28"/>
       <c r="S24" s="33" t="s">
         <v>43</v>
@@ -3580,7 +4598,7 @@
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B25" s="77" t="s">
+      <c r="B25" s="78" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="32" t="str">
@@ -3623,7 +4641,10 @@
       <c r="O25" s="50">
         <v>18</v>
       </c>
-      <c r="P25" s="25"/>
+      <c r="P25" s="25">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="S25" s="33" t="s">
         <v>45</v>
       </c>
@@ -3632,7 +4653,7 @@
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B26" s="78"/>
+      <c r="B26" s="79"/>
       <c r="C26" s="34" t="str">
         <f>IF(C23="","NA",C23)</f>
         <v>Maria</v>
@@ -3673,7 +4694,10 @@
       <c r="O26" s="52">
         <v>13</v>
       </c>
-      <c r="P26" s="27"/>
+      <c r="P26" s="27">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
+      </c>
       <c r="S26" s="33" t="s">
         <v>46</v>
       </c>
@@ -3682,9 +4706,9 @@
       </c>
     </row>
     <row r="27" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="78"/>
+      <c r="B27" s="79"/>
       <c r="C27" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Ana</v>
       </c>
       <c r="D27" s="55">
@@ -3723,7 +4747,10 @@
       <c r="O27" s="56">
         <v>14</v>
       </c>
-      <c r="P27" s="36"/>
+      <c r="P27" s="36">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="S27" s="33" t="s">
         <v>47</v>
       </c>
@@ -3732,32 +4759,32 @@
       </c>
     </row>
     <row r="28" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="80" t="s">
+      <c r="B28" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="81"/>
+      <c r="C28" s="83"/>
       <c r="D28" s="37">
         <f>SUM(D16:D27)</f>
         <v>119</v>
       </c>
       <c r="E28" s="37">
-        <f t="shared" ref="E28:O28" si="1">SUM(E16:E27)</f>
+        <f t="shared" ref="E28:O28" si="2">SUM(E16:E27)</f>
         <v>121</v>
       </c>
       <c r="F28" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>127</v>
       </c>
       <c r="G28" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>116</v>
       </c>
       <c r="H28" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="I28" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>129</v>
       </c>
       <c r="J28" s="37">
@@ -3765,29 +4792,32 @@
         <v>89</v>
       </c>
       <c r="K28" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>111</v>
       </c>
       <c r="L28" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>144</v>
       </c>
       <c r="M28" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>115</v>
       </c>
       <c r="N28" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>137</v>
       </c>
       <c r="O28" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>148</v>
       </c>
-      <c r="P28" s="39"/>
+      <c r="P28" s="39">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B29" s="82" t="s">
+      <c r="B29" s="84" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="32" t="str">
@@ -3830,10 +4860,13 @@
       <c r="O29" s="58">
         <v>4</v>
       </c>
-      <c r="P29" s="40"/>
+      <c r="P29" s="40">
+        <f t="shared" si="0"/>
+        <v>1.8333333333333333</v>
+      </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B30" s="82"/>
+      <c r="B30" s="84"/>
       <c r="C30" s="34" t="str">
         <f>IF(C17="","NA",C17)</f>
         <v>Maria</v>
@@ -3874,10 +4907,13 @@
       <c r="O30" s="60">
         <v>2</v>
       </c>
-      <c r="P30" s="41"/>
+      <c r="P30" s="41">
+        <f t="shared" si="0"/>
+        <v>2.1666666666666665</v>
+      </c>
     </row>
     <row r="31" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="82"/>
+      <c r="B31" s="84"/>
       <c r="C31" s="35" t="str">
         <f>IF(C18="","NA",C18)</f>
         <v>Ana</v>
@@ -3918,62 +4954,68 @@
       <c r="O31" s="62">
         <v>2</v>
       </c>
-      <c r="P31" s="42"/>
+      <c r="P31" s="42">
+        <f t="shared" si="0"/>
+        <v>2.25</v>
+      </c>
     </row>
     <row r="32" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="83" t="s">
+      <c r="B32" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="84"/>
+      <c r="C32" s="86"/>
       <c r="D32" s="43">
         <f>SUM(D28:D31)</f>
         <v>122</v>
       </c>
       <c r="E32" s="43">
-        <f t="shared" ref="E32:O32" si="2">SUM(E28:E31)</f>
+        <f t="shared" ref="E32:O32" si="3">SUM(E28:E31)</f>
         <v>128</v>
       </c>
       <c r="F32" s="43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>131</v>
       </c>
       <c r="G32" s="43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>122</v>
       </c>
       <c r="H32" s="43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="I32" s="43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>140</v>
       </c>
       <c r="J32" s="43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>99</v>
       </c>
       <c r="K32" s="43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>116</v>
       </c>
       <c r="L32" s="43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>149</v>
       </c>
       <c r="M32" s="43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>123</v>
       </c>
       <c r="N32" s="43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>139</v>
       </c>
       <c r="O32" s="44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>156</v>
       </c>
-      <c r="P32" s="45"/>
+      <c r="P32" s="45">
+        <f t="shared" si="0"/>
+        <v>126.25</v>
+      </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="D34" s="46" t="s">
@@ -4014,48 +5056,115 @@
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B35" s="76" t="s">
+      <c r="B35" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="76"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="47"/>
+      <c r="C35" s="81"/>
+      <c r="D35" s="47">
+        <f>SUM(D29:D31)/D28</f>
+        <v>2.5210084033613446E-2</v>
+      </c>
+      <c r="E35" s="47">
+        <f t="shared" ref="E35:O35" si="4">SUM(E29:E31)/E28</f>
+        <v>5.7851239669421489E-2</v>
+      </c>
+      <c r="F35" s="47">
+        <f t="shared" si="4"/>
+        <v>3.1496062992125984E-2</v>
+      </c>
+      <c r="G35" s="47">
+        <f t="shared" si="4"/>
+        <v>5.1724137931034482E-2</v>
+      </c>
+      <c r="H35" s="47">
+        <f t="shared" si="4"/>
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="I35" s="47">
+        <f t="shared" si="4"/>
+        <v>8.5271317829457363E-2</v>
+      </c>
+      <c r="J35" s="47">
+        <f t="shared" si="4"/>
+        <v>0.11235955056179775</v>
+      </c>
+      <c r="K35" s="47">
+        <f t="shared" si="4"/>
+        <v>4.5045045045045043E-2</v>
+      </c>
+      <c r="L35" s="47">
+        <f t="shared" si="4"/>
+        <v>3.4722222222222224E-2</v>
+      </c>
+      <c r="M35" s="47">
+        <f t="shared" si="4"/>
+        <v>6.9565217391304349E-2</v>
+      </c>
+      <c r="N35" s="47">
+        <f t="shared" si="4"/>
+        <v>1.4598540145985401E-2</v>
+      </c>
+      <c r="O35" s="47">
+        <f t="shared" si="4"/>
+        <v>5.4054054054054057E-2</v>
+      </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B36" s="76" t="s">
+      <c r="B36" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="76"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
-      <c r="J36" s="47"/>
-      <c r="K36" s="47"/>
-      <c r="L36" s="47"/>
-      <c r="M36" s="47"/>
-      <c r="N36" s="47"/>
-      <c r="O36" s="47"/>
+      <c r="C36" s="81"/>
+      <c r="D36" s="48">
+        <f>SUM($D$29:D$31) / SUM($D$28:D$28)</f>
+        <v>2.5210084033613446E-2</v>
+      </c>
+      <c r="E36" s="47">
+        <f>SUM($D$29:E$31) / SUM($D$28:E$28)</f>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F36" s="47">
+        <f>SUM($D$29:F$31) / SUM($D$28:F$28)</f>
+        <v>3.8147138964577658E-2</v>
+      </c>
+      <c r="G36" s="47">
+        <f>SUM($D$29:G$31) / SUM($D$28:G$28)</f>
+        <v>4.1407867494824016E-2</v>
+      </c>
+      <c r="H36" s="47">
+        <f>SUM($D$29:H$31) / SUM($D$28:H$28)</f>
+        <v>4.585537918871252E-2</v>
+      </c>
+      <c r="I36" s="47">
+        <f>SUM($D$29:I$31) / SUM($D$28:I$28)</f>
+        <v>5.3160919540229883E-2</v>
+      </c>
+      <c r="J36" s="47">
+        <f>SUM($D$29:J$31) / SUM($D$28:J$28)</f>
+        <v>5.9872611464968153E-2</v>
+      </c>
+      <c r="K36" s="47">
+        <f>SUM($D$29:K$31) / SUM($D$28:K$28)</f>
+        <v>5.8035714285714288E-2</v>
+      </c>
+      <c r="L36" s="47">
+        <f>SUM($D$29:L$31) / SUM($D$28:L$28)</f>
+        <v>5.4807692307692307E-2</v>
+      </c>
+      <c r="M36" s="47">
+        <f>SUM($D$29:M$31) / SUM($D$28:M$28)</f>
+        <v>5.627705627705628E-2</v>
+      </c>
+      <c r="N36" s="47">
+        <f>SUM($D$29:N$31) / SUM($D$28:N$28)</f>
+        <v>5.1857585139318887E-2</v>
+      </c>
+      <c r="O36" s="47">
+        <f>SUM($D$29:O$31) / SUM($D$28:O$28)</f>
+        <v>5.2083333333333336E-2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B2:Q6"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B19:B21"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B22:B24"/>
@@ -4063,14 +5172,24 @@
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:B31"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B2:Q6"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B19:B21"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O13:P13" xr:uid="{C1E85C68-2F8F-41C6-B929-A134D32524B4}">
+      <formula1>$S$19:$S$27</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:T36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4221,14 +5340,14 @@
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B13" s="17"/>
-      <c r="M13" s="85" t="s">
+      <c r="M13" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="N13" s="85"/>
-      <c r="O13" s="86" t="s">
+      <c r="N13" s="76"/>
+      <c r="O13" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="P13" s="86"/>
+      <c r="P13" s="77"/>
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4322,7 +5441,7 @@
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B16" s="77" t="s">
+      <c r="B16" s="78" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="24" t="s">
@@ -4370,7 +5489,7 @@
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B17" s="78"/>
+      <c r="B17" s="79"/>
       <c r="C17" s="26" t="s">
         <v>31</v>
       </c>
@@ -4417,7 +5536,7 @@
       <c r="Q17" s="28"/>
     </row>
     <row r="18" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="79"/>
+      <c r="B18" s="80"/>
       <c r="C18" s="29" t="s">
         <v>33</v>
       </c>
@@ -4470,7 +5589,7 @@
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B19" s="77" t="s">
+      <c r="B19" s="78" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="32" t="str">
@@ -4526,7 +5645,7 @@
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B20" s="78"/>
+      <c r="B20" s="79"/>
       <c r="C20" s="34" t="str">
         <f t="shared" ref="C20:C27" si="1">IF(C17="","NA",C17)</f>
         <v>Maria</v>
@@ -4580,7 +5699,7 @@
       </c>
     </row>
     <row r="21" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="79"/>
+      <c r="B21" s="80"/>
       <c r="C21" s="35" t="str">
         <f t="shared" si="1"/>
         <v>Ana</v>
@@ -4634,7 +5753,7 @@
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B22" s="77" t="s">
+      <c r="B22" s="78" t="s">
         <v>40</v>
       </c>
       <c r="C22" s="32" t="str">
@@ -4690,7 +5809,7 @@
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B23" s="78"/>
+      <c r="B23" s="79"/>
       <c r="C23" s="34" t="str">
         <f t="shared" si="1"/>
         <v>Maria</v>
@@ -4744,7 +5863,7 @@
       </c>
     </row>
     <row r="24" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="79"/>
+      <c r="B24" s="80"/>
       <c r="C24" s="35" t="str">
         <f t="shared" si="1"/>
         <v>Ana</v>
@@ -4798,7 +5917,7 @@
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B25" s="77" t="s">
+      <c r="B25" s="78" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="32" t="str">
@@ -4853,7 +5972,7 @@
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B26" s="78"/>
+      <c r="B26" s="79"/>
       <c r="C26" s="34" t="str">
         <f>IF(C23="","NA",C23)</f>
         <v>Maria</v>
@@ -4906,7 +6025,7 @@
       </c>
     </row>
     <row r="27" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="78"/>
+      <c r="B27" s="79"/>
       <c r="C27" s="35" t="str">
         <f t="shared" si="1"/>
         <v>Ana</v>
@@ -4959,10 +6078,10 @@
       </c>
     </row>
     <row r="28" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="80" t="s">
+      <c r="B28" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="81"/>
+      <c r="C28" s="83"/>
       <c r="D28" s="37">
         <f>SUM(D16:D27)</f>
         <v>119</v>
@@ -5017,7 +6136,7 @@
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B29" s="82" t="s">
+      <c r="B29" s="84" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="32" t="str">
@@ -5066,7 +6185,7 @@
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B30" s="82"/>
+      <c r="B30" s="84"/>
       <c r="C30" s="34" t="str">
         <f>IF(C17="","NA",C17)</f>
         <v>Maria</v>
@@ -5113,7 +6232,7 @@
       </c>
     </row>
     <row r="31" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="82"/>
+      <c r="B31" s="84"/>
       <c r="C31" s="35" t="str">
         <f>IF(C18="","NA",C18)</f>
         <v>Ana</v>
@@ -5160,10 +6279,10 @@
       </c>
     </row>
     <row r="32" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="83" t="s">
+      <c r="B32" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="84"/>
+      <c r="C32" s="86"/>
       <c r="D32" s="43">
         <f>SUM(D28:D31)</f>
         <v>122</v>
@@ -5256,10 +6375,10 @@
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B35" s="76" t="s">
+      <c r="B35" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="76"/>
+      <c r="C35" s="81"/>
       <c r="D35" s="47">
         <f>SUM(D29:D31)/D32</f>
         <v>2.4590163934426229E-2</v>
@@ -5310,10 +6429,10 @@
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B36" s="76" t="s">
+      <c r="B36" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="76"/>
+      <c r="C36" s="81"/>
       <c r="D36" s="48">
         <f>D35</f>
         <v>2.4590163934426229E-2</v>
@@ -5365,11 +6484,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B2:Q6"/>
     <mergeCell ref="M13:N13"/>
@@ -5377,9 +6491,14 @@
     <mergeCell ref="B16:B18"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O13:P13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O13:P13" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>$S$19:$S$27</formula1>
     </dataValidation>
   </dataValidations>
